--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260606_205612.xlsx
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
